--- a/data/public_wireless_lan/data.xlsx
+++ b/data/public_wireless_lan/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,13 +460,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="str">
-        <v>34.34911337642227</v>
+        <v>34.42222463856056</v>
       </c>
       <c r="C2" t="str">
-        <v>134.05062987786422</v>
+        <v>134.05413144104674</v>
       </c>
       <c r="D2" t="str">
         <v>37201</v>
@@ -481,7 +481,7 @@
         <v>高松市</v>
       </c>
       <c r="H2" t="str">
-        <v>玉藻公園披雲閣</v>
+        <v>男木交流館</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -490,7 +490,7 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>香川県高松市玉藻町２番１号</v>
+        <v>香川県高松市男木町１９８６番地</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -519,13 +519,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="str">
-        <v>34.42222463856056</v>
+        <v>34.38949764744894</v>
       </c>
       <c r="C3" t="str">
-        <v>134.05413144104674</v>
+        <v>134.05238501219824</v>
       </c>
       <c r="D3" t="str">
         <v>37201</v>
@@ -540,7 +540,7 @@
         <v>高松市</v>
       </c>
       <c r="H3" t="str">
-        <v>男木交流館</v>
+        <v>鬼ヶ島おにの館</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -549,7 +549,7 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>香川県高松市男木町１９８６番地</v>
+        <v>香川県高松市女木町１５番地２２</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -578,13 +578,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="str">
-        <v>34.38949764744894</v>
+        <v>34.17037598630636</v>
       </c>
       <c r="C4" t="str">
-        <v>134.05238501219824</v>
+        <v>134.08232722876988</v>
       </c>
       <c r="D4" t="str">
         <v>37201</v>
@@ -599,7 +599,7 @@
         <v>高松市</v>
       </c>
       <c r="H4" t="str">
-        <v>鬼ヶ島おにの館</v>
+        <v>塩江インフォメーションセンター</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -608,7 +608,7 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>香川県高松市女木町１５番地２２</v>
+        <v>香川県高松市塩江町安原上東３９０−９</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -632,189 +632,12 @@
         <v/>
       </c>
       <c r="S4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>9</v>
-      </c>
-      <c r="B5" t="str">
-        <v>34.17037598630636</v>
-      </c>
-      <c r="C5" t="str">
-        <v>134.08232722876988</v>
-      </c>
-      <c r="D5" t="str">
-        <v>37201</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>香川県</v>
-      </c>
-      <c r="G5" t="str">
-        <v>高松市</v>
-      </c>
-      <c r="H5" t="str">
-        <v>塩江インフォメーションセンター</v>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v>香川県高松市塩江町安原上東３９０−９</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v>KAGAWA-WiFi</v>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-      <c r="R5" t="str">
-        <v/>
-      </c>
-      <c r="S5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>10</v>
-      </c>
-      <c r="B6" t="str">
-        <v>34.40944181761771</v>
-      </c>
-      <c r="C6" t="str">
-        <v>134.10690956498806</v>
-      </c>
-      <c r="D6" t="str">
-        <v>37201</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>香川県</v>
-      </c>
-      <c r="G6" t="str">
-        <v>高松市</v>
-      </c>
-      <c r="H6" t="str">
-        <v>眉山亭</v>
-      </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v>香川県高松市庵治町６０３４</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v>KAGAWA-WiFi</v>
-      </c>
-      <c r="Q6" t="str">
-        <v/>
-      </c>
-      <c r="R6" t="str">
-        <v/>
-      </c>
-      <c r="S6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>11</v>
-      </c>
-      <c r="B7" t="str">
-        <v>34.35903506013678</v>
-      </c>
-      <c r="C7" t="str">
-        <v>134.1021938648672</v>
-      </c>
-      <c r="D7" t="str">
-        <v>37201</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v>香川県</v>
-      </c>
-      <c r="G7" t="str">
-        <v>高松市</v>
-      </c>
-      <c r="H7" t="str">
-        <v>屋島山上時計案内板</v>
-      </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v>香川県高松市屋島東町</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v>KAGAWA-WiFi</v>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S4"/>
   </ignoredErrors>
 </worksheet>
 </file>